--- a/EIANN/data/supplementary_tables/Table_S7_spiral_hyperparams.xlsx
+++ b/EIANN/data/supplementary_tables/Table_S7_spiral_hyperparams.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,28 +437,40 @@
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Feedforward ANN 
+(no bias)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Backprop (EIANN) 
+(no bias)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Dend Target Prop 
+(no bias)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Feedforward ANN 
 (no hidden  layers)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Feedforward ANN 
 (learned bias)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Feedforward ANN 
-(no bias)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Backprop (EIANN) 
 (learned bias)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Dend Target Prop 
 (learned bias)</t>
@@ -468,147 +480,183 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Winit (Output)</t>
+          <t>W_init (H1)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.386548065293654</v>
+        <v>0.7661562722497335</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5433568834277912</v>
+        <v>0.6131275385411309</v>
       </c>
       <c r="D2" t="n">
-        <v>3.518843703166975</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5.977812184651836</v>
+        <v>2.401295546297699</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>5.42693091561223</v>
+        <v>3.092179371471005</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.327218040830208</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.744225231975699</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>η, W (Output)</t>
+          <t>η, W (H1)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08158367762594287</v>
+        <v>0.008671959543266558</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01080926960544266</v>
+        <v>0.01344811271920673</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001309333856710242</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.6722278010177094</v>
+        <v>0.07091479862034537</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>0.09769059583309837</v>
+        <v>0.2344242206840233</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1769523365865042</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.08563556008428913</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Winit (H1)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>W_init (H2)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.1340356807870724</v>
       </c>
       <c r="C4" t="n">
-        <v>3.092179371471005</v>
+        <v>0.2417308848321429</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7661562722497335</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2.327218040830208</v>
+        <v>1.18872021416561</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>3.744225231975699</v>
+        <v>1.068480127016743</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.183393888582326</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.396275790739738</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>η, W (H1)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>η, W (H2)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.008671959543266558</v>
       </c>
       <c r="C5" t="n">
+        <v>0.01344811271920673</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.07091479862034537</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>0.2344242206840233</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.008671959543266558</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>0.1769523365865042</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>0.08563556008428913</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Winit (H2)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>W_init (Output)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.518843703166975</v>
       </c>
       <c r="C6" t="n">
-        <v>1.068480127016743</v>
+        <v>1.876311287872052</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1340356807870724</v>
+        <v>2.027682194987855</v>
       </c>
       <c r="E6" t="n">
-        <v>5.183393888582326</v>
+        <v>5.386548065293654</v>
       </c>
       <c r="F6" t="n">
-        <v>3.396275790739738</v>
+        <v>0.5433568834277912</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.977812184651836</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.42693091561223</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>η, W (H2)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>η, W (Output)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.001309333856710242</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2344242206840233</v>
+        <v>0.03718742430289554</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008671959543266558</v>
+        <v>0.008067175133788176</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1769523365865042</v>
+        <v>0.08158367762594287</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08563556008428913</v>
+        <v>0.01080926960544266</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6722278010177094</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.09769059583309837</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Yinit (SomaI, H1)</t>
+          <t>Y_init (SomaI, H1)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -616,27 +664,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
+      <c r="C8" t="n">
+        <v>0.09433188698616012</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.079549779847814</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>4.708083116173457</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
         <v>1.717071876658599</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Winit (SomaI, H1)</t>
+          <t>W_init (SomaI, H1)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -644,27 +698,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
+      <c r="C9" t="n">
+        <v>0.2633981316147314</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.913752133104837</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>1.064629862199998</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>8.526807327982732</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Qinit (SomaI, H1)</t>
+          <t>Q_init (SomaI, H1)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -672,27 +732,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
+      <c r="C10" t="n">
+        <v>0.1268136440609127</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.6140729287494098</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
         <v>0.7308804739762219</v>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
         <v>2.5572584153779</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rinit (SomaI, H1)</t>
+          <t>R_init (SomaI, H1)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -700,27 +766,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
+      <c r="C11" t="n">
+        <v>0.9137983373562025</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.033007401134379</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
         <v>1.985595933356355</v>
       </c>
-      <c r="F11" t="n">
+      <c r="H11" t="n">
         <v>3.821257280968513</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Yinit (SomaI, H2)</t>
+          <t>Y_init (SomaI, H2)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -728,27 +800,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
+      <c r="C12" t="n">
+        <v>0.08379437739573734</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5499413114134734</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
         <v>3.273971082147326</v>
       </c>
-      <c r="F12" t="n">
+      <c r="H12" t="n">
         <v>1.961562817177921</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Winit (SomaI, H2)</t>
+          <t>W_init (SomaI, H2)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -756,27 +834,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
+      <c r="C13" t="n">
+        <v>0.3013595225808092</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.837361344289605</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
         <v>3.386558310279101</v>
       </c>
-      <c r="F13" t="n">
+      <c r="H13" t="n">
         <v>3.356842824473377</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Qinit (SomaI, H2)</t>
+          <t>Q_init (SomaI, H2)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -784,27 +868,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
+      <c r="C14" t="n">
+        <v>2.250163572933602</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.8915120547270652</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
         <v>0.6920399968903772</v>
       </c>
-      <c r="F14" t="n">
+      <c r="H14" t="n">
         <v>2.672772790852625</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rinit (SomaI, H2)</t>
+          <t>R_init (SomaI, H2)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -812,27 +902,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
+      <c r="C15" t="n">
+        <v>1.206686448067799</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.680091294469877</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
         <v>1.656403773484931</v>
       </c>
-      <c r="F15" t="n">
+      <c r="H15" t="n">
         <v>2.527793096667097</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Yinit (SomaI, Output)</t>
+          <t>Y_init (SomaI, Output)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -840,27 +936,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
+      <c r="C16" t="n">
+        <v>0.2625422924190216</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.505594142433112</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
         <v>1.762993057568605</v>
       </c>
-      <c r="F16" t="n">
+      <c r="H16" t="n">
         <v>1.114662304188637</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Winit (SomaI, Output)</t>
+          <t>W_init (SomaI, Output)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -868,27 +970,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
+      <c r="C17" t="n">
+        <v>0.5409982149056294</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.3034932643638723</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
         <v>2.289938249676595</v>
       </c>
-      <c r="F17" t="n">
+      <c r="H17" t="n">
         <v>1.982369341320862</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Qinit (SomaI, Output)</t>
+          <t>Q_init (SomaI, Output)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -896,27 +1004,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
+      <c r="C18" t="n">
+        <v>0.1217279620800388</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.06932742253127393</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
         <v>1.460040157290248</v>
       </c>
-      <c r="F18" t="n">
+      <c r="H18" t="n">
         <v>0.9622943352611545</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rinit (SomaI, Output)</t>
+          <t>R_init (SomaI, Output)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -924,27 +1038,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
+      <c r="C19" t="n">
+        <v>1.780520079365352</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.7752282811624321</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
         <v>1.559187825960845</v>
       </c>
-      <c r="F19" t="n">
+      <c r="H19" t="n">
         <v>3.924537045484193</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Yinit (DendI, H1)</t>
+          <t>Y_init (DendI, H1)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -957,17 +1077,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D20" t="n">
+        <v>0.6956827403710787</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
         <v>0.7284678918500063</v>
       </c>
     </row>
@@ -987,24 +1115,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D21" t="n">
+        <v>0.1001120320314592</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
         <v>0.2101712344149589</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bscale (H1)</t>
+          <t>B_scale (H1)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1017,17 +1153,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D22" t="n">
+        <v>0.4226775539087423</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
         <v>0.1879267248852734</v>
       </c>
     </row>
@@ -1047,24 +1191,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D23" t="n">
+        <v>0.0952585373676334</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
         <v>0.08025562647850921</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Qsum (DendI, H1)</t>
+          <t>Q_sum (DendI, H1)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1077,17 +1229,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D24" t="n">
+        <v>22.95720359542291</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
         <v>9.419321612663568</v>
       </c>
     </row>
@@ -1107,24 +1267,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D25" t="n">
+        <v>0.03435512003722571</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
         <v>0.01343573403768564</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rsum (DendI, H1)</t>
+          <t>R_sum (DendI, H1)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1137,24 +1305,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D26" t="n">
+        <v>1.945052260741741</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
         <v>1.171246432090221</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Yinit (DendI, H2)</t>
+          <t>Y_init (DendI, H2)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1167,17 +1343,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D27" t="n">
+        <v>2.319998656803615</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
         <v>2.713538702536155</v>
       </c>
     </row>
@@ -1197,24 +1381,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D28" t="n">
+        <v>0.1001120320314592</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
         <v>0.2101712344149589</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Bscale (H2)</t>
+          <t>B_scale (H2)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1227,17 +1419,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D29" t="n">
+        <v>0.3319987552558894</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
         <v>0.7149623055734934</v>
       </c>
     </row>
@@ -1257,24 +1457,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D30" t="n">
+        <v>0.0952585373676334</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
         <v>0.08025562647850921</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Qsum (DendI, H2)</t>
+          <t>Q_sum (DendI, H2)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1287,17 +1495,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D31" t="n">
+        <v>3.481537410204755</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
         <v>11.68995252240356</v>
       </c>
     </row>
@@ -1317,24 +1533,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D32" t="n">
+        <v>0.03435512003722571</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
         <v>0.01343573403768564</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rsum (DendI, H2)</t>
+          <t>R_sum (DendI, H2)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1347,18 +1571,132 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D33" t="n">
+        <v>1.383998436163171</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
         <v>2.147366810208358</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>η, bias (Output)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.000494197567654425</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.06332269100152069</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.0129479264155026</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.004577231612808623</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>η, bias (H1)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0.09062365730598693</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.008451149236900886</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.02506348415291213</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>η, bias (H2)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0.09062365730598693</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.008451149236900886</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.02506348415291213</v>
       </c>
     </row>
   </sheetData>
